--- a/stories/arbres/ATOM-EMO.LEX.008-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Georges verse l'eau. Le verre penche. L'eau mouille la table. Georges sent ses joues chaudes. Il dit : je suis gêné. Papa dit : c'est une erreur. Une erreur, ce n'est pas toi. Georges dit : j'ai versé. Il prend un chiffon. Il répare. La table redevient sèche. Plus tard, au salon, Georges bouscule un puzzle. Une pièce tombe. Il est gêné. Il dit l'erreur. Il pose la pièce. Il répare. Maman sourit. Même leçon, autre pièce. On dit. On répare.</t>
+          <t>Georges verse l'eau. Le verre penche. L'eau mouille la table. Georges sent ses joues chaudes. Je suis gêné. C'est une erreur. Une erreur, ce n'est pas toi. J'ai versé. Il prend un chiffon. Il répare. La table redevient sèche. Plus tard, au salon, Georges bouscule un puzzle. Une pièce tombe. Il est gêné. Il dit l'erreur. Il pose la pièce. Il répare. Maman sourit. Même leçon, autre pièce. On dit. On répare.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Georges verse l'eau. Le verre penche. L'eau mouille la table. Georges sent ses joues chaudes.
+narrateur|Je suis gêné.
+papa|C'est une erreur.
+narrateur|Une erreur, ce n'est pas toi.
+enfant-m|J'ai versé.
+narrateur|Il prend un chiffon. Il répare. La table redevient sèche. Plus tard, au salon, Georges bouscule un puzzle. Une pièce tombe. Il est gêné. Il dit l'erreur. Il pose la pièce. Il répare. Maman sourit. Même leçon, autre pièce. On dit. On répare.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Georges a les joues chaudes. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Georges était gêné. Il a dit l'erreur. Il a réparé. Papa et maman ont écouté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Georges plie le chiffon. Le puzzle est de nouveau entier.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 narrateur|Il prend un chiffon. Il répare. La table redevient sèche. Plus tard, au salon, Georges bouscule un puzzle. Une pièce tombe. Il est gêné. Il dit l'erreur. Il pose la pièce. Il répare. Maman sourit. Même leçon, autre pièce. On dit. On répare.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Georges a les joues chaudes. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Georges était gêné. Il a dit l'erreur. Il a réparé. Papa et maman ont écouté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Georges plie le chiffon. Le puzzle est de nouveau entier.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.008-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Georges est gêné, puis il répare</t>
+          <t>L'eau de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nino verse de l'eau. Il dit qu'il est gêné. Il répare. Plus tard, une pièce de puzzle. Il dit encore. Il répare.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Georges verse l'eau. Le verre penche. L'eau mouille la table. Georges sent ses joues chaudes. Je suis gêné. C'est une erreur. Une erreur, ce n'est pas toi. J'ai versé. Il prend un chiffon. Il répare. La table redevient sèche. Plus tard, au salon, Georges bouscule un puzzle. Une pièce tombe. Il est gêné. Il dit l'erreur. Il pose la pièce. Il répare. Maman sourit. Même leçon, autre pièce. On dit. On répare.</t>
+          <t>La vitre de la cuisine a de la buée. Un doigt y a dessiné une petite goutte. Ça sent la soupe, tout chaud. La bouilloire fait tic, tic, tic. Un torchon humide pend au dossier. La table a un tapis à carreaux. La soupe est presque prête, Nino. On met l'eau, tout doucement. La vitre est floue, papa. C'est la buée. C'est chaud. Tu portes le petit verre ? Oui. Il est froid. On reste près de la table. En ce moment, Nino verse l'eau. Le verre penche. L'eau glisse sur le tapis à carreaux. Une flaque ronde brille. Nino sent ses joues chaudes. Il baisse un peu le menton. Je suis gêné. C'est une erreur. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé. Voici le torchon. Je veux réparer. Nino essuie la table. Le torchon devient plus lourd. La flaque disparaît. La table redevient sèche. Merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer. Bravo, Nino. Plus tard, le salon est calme. Un puzzle attend sur le tapis. Une pièce bleue brille. Nino s'assoit près du puzzle. Son genou touche une pièce. La pièce tombe sur le tapis. Les joues de Nino chauffent encore. Je suis gêné. J'ai bougé la pièce. C'est une erreur. On peut la dire. Puis réparer. Je veux réparer. Nino pose la pièce à sa place. Le bleu retrouve le bleu. Tu as dit. Tu as réparé. Même leçon, autre pièce. On dit. On répare. Le puzzle redevient entier. La buée sèche un peu, là-bas.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,12 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Georges verse l'eau. Le verre penche. L'eau mouille la table. Georges sent ses joues chaudes.
-narrateur|Je suis gêné.
+          <t>narrateur|La vitre de la cuisine a de la buée.
+narrateur|Un doigt y a dessiné une petite goutte.
+narrateur|Ça sent la soupe, tout chaud.
+narrateur|La bouilloire fait tic, tic, tic.
+narrateur|Un torchon humide pend au dossier.
+narrateur|La table a un tapis à carreaux.
+maman|La soupe est presque prête, Nino.
+papa|On met l'eau, tout doucement.
+enfant-m|La vitre est floue, papa.
+papa|C'est la buée. C'est chaud.
+maman|Tu portes le petit verre ?
+enfant-m|Oui. Il est froid.
+papa|On reste près de la table.
+narrateur|En ce moment, Nino verse l'eau.
+narrateur|Le verre penche.
+narrateur|L'eau glisse sur le tapis à carreaux.
+narrateur|Une flaque ronde brille.
+narrateur|Nino sent ses joues chaudes.
+narrateur|Il baisse un peu le menton.
+enfant-m|Je suis gêné.
 papa|C'est une erreur.
-narrateur|Une erreur, ce n'est pas toi.
+papa|Une erreur, ce n'est pas toi.
+maman|L'erreur, on peut la dire.
 enfant-m|J'ai versé.
-narrateur|Il prend un chiffon. Il répare. La table redevient sèche. Plus tard, au salon, Georges bouscule un puzzle. Une pièce tombe. Il est gêné. Il dit l'erreur. Il pose la pièce. Il répare. Maman sourit. Même leçon, autre pièce. On dit. On répare.</t>
+papa|Voici le torchon.
+enfant-m|Je veux réparer.
+narrateur|Nino essuie la table.
+narrateur|Le torchon devient plus lourd.
+narrateur|La flaque disparaît.
+maman|La table redevient sèche.
+papa|Merci d'avoir dit.
+papa|Être gêné, on le dit.
+maman|Puis on peut réparer.
+papa|Bravo, Nino.
+narrateur|Plus tard, le salon est calme.
+narrateur|Un puzzle attend sur le tapis.
+narrateur|Une pièce bleue brille.
+narrateur|Nino s'assoit près du puzzle.
+narrateur|Son genou touche une pièce.
+narrateur|La pièce tombe sur le tapis.
+narrateur|Les joues de Nino chauffent encore.
+enfant-m|Je suis gêné.
+enfant-m|J'ai bougé la pièce.
+maman|C'est une erreur.
+papa|On peut la dire. Puis réparer.
+enfant-m|Je veux réparer.
+narrateur|Nino pose la pièce à sa place.
+narrateur|Le bleu retrouve le bleu.
+maman|Tu as dit. Tu as réparé.
+papa|Même leçon, autre pièce.
+enfant-m|On dit. On répare.
+narrateur|Le puzzle redevient entier.
+narrateur|La buée sèche un peu, là-bas.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1345,7 +1404,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Georges a les joues chaudes. Que fait-il ?</t>
+          <t>Nino a les joues chaudes. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1422,14 +1481,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1501,7 +1560,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Georges a les joues chaudes. Que fait-il ?</t>
+          <t>narrateur|Nino a les joues chaudes.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1529,7 +1589,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Georges était gêné. Il a dit l'erreur. Il a réparé. Papa et maman ont écouté.</t>
+          <t>Nino était gêné. Il a dit l'erreur. Il a réparé. Papa et maman ont écouté. J'ai versé. Puis j'ai essuyé. Oui. Tu as nommé : gêné. Puis tu as réparé le puzzle. Bravo. C'est du bon travail. L'erreur n'est pas moi. C'est ça. L'erreur, on la dit. Le torchon est plié sur la table. La pièce bleue est à sa place. On dit. On répare. Deux fois. L'eau, puis la pièce. Même leçon, autre moment. La soupe sent encore, tout doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1590,14 +1650,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1673,7 +1733,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Georges était gêné. Il a dit l'erreur. Il a réparé. Papa et maman ont écouté.</t>
+          <t>narrateur|Nino était gêné.
+narrateur|Il a dit l'erreur.
+narrateur|Il a réparé.
+narrateur|Papa et maman ont écouté.
+enfant-m|J'ai versé. Puis j'ai essuyé.
+papa|Oui. Tu as nommé : gêné.
+maman|Puis tu as réparé le puzzle.
+papa|Bravo. C'est du bon travail.
+enfant-m|L'erreur n'est pas moi.
+maman|C'est ça. L'erreur, on la dit.
+narrateur|Le torchon est plié sur la table.
+narrateur|La pièce bleue est à sa place.
+papa|On dit. On répare.
+enfant-m|Deux fois. L'eau, puis la pièce.
+maman|Même leçon, autre moment.
+narrateur|La soupe sent encore, tout doux.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1701,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Georges plie le chiffon. Le puzzle est de nouveau entier.</t>
+          <t>Nino plie le torchon. Le puzzle est de nouveau entier. On pose le torchon près de l'évier ? Oui, papa. La table est sèche. Merci, Nino. J'ai réparé. Tu as dit, aussi. On goûte la soupe, tout à l'heure ? Oui. Elle sent bon. Nino touche la pièce bleue. Elle est un peu rugueuse. Elle est à sa place. Je suis moins gêné. On a réparé. C'est bien. La buée a presque disparu. Un rond clair est sur la vitre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1762,14 +1837,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1837,7 +1912,22 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Georges plie le chiffon. Le puzzle est de nouveau entier.</t>
+          <t>narrateur|Nino plie le torchon.
+narrateur|Le puzzle est de nouveau entier.
+papa|On pose le torchon près de l'évier ?
+enfant-m|Oui, papa.
+maman|La table est sèche. Merci, Nino.
+enfant-m|J'ai réparé.
+papa|Tu as dit, aussi.
+maman|On goûte la soupe, tout à l'heure ?
+enfant-m|Oui. Elle sent bon.
+narrateur|Nino touche la pièce bleue.
+narrateur|Elle est un peu rugueuse.
+papa|Elle est à sa place.
+enfant-m|Je suis moins gêné.
+maman|On a réparé. C'est bien.
+narrateur|La buée a presque disparu.
+narrateur|Un rond clair est sur la vitre.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1865,7 +1955,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais gêné. J'ai dit. Tu as réparé. Bravo. L'eau, puis la pièce. Pareil. Le torchon reste plié. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1926,14 +2016,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2005,7 +2095,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'étais gêné. J'ai dit.
+papa|Tu as réparé. Bravo.
+maman|L'eau, puis la pièce. Pareil.
+narrateur|Le torchon reste plié.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2027,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2159,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-07.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Georges verse l'eau. Le verre penche. L'eau mouille la table. Georges sent ses joues chaudes. Il dit : je suis &lt;emphasis level="moderate"&gt;gêné&lt;/emphasis&gt;. Papa dit : c'est une erreur. Une erreur, ce n'est pas toi. Georges dit : j'ai versé. Il prend un chiffon. Il répare. La table redevient sèche. Plus tard, au salon, Georges bouscule un puzzle. Une pièce tombe. Il est gêné. Il dit l'erreur. Il pose la pièce. Il répare. Maman sourit. Même leçon, autre pièce. On dit. On répare.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vitre de la cuisine a de la buée. Un doigt y a dessiné une petite goutte. Ça sent la soupe, tout chaud. La bouilloire fait tic, tic, tic. Un torchon humide pend au dossier. La table a un tapis à carreaux. La soupe est presque prête, Nino. On met l'eau, tout doucement. La vitre est floue, papa. C'est la buée. C'est chaud. Tu portes le petit verre ? Oui. Il est froid. On reste près de la table. En ce moment, Nino verse l'eau. Le verre penche. L'eau glisse sur le tapis à carreaux. Une flaque ronde brille. Nino sent ses joues chaudes. Il baisse un peu le menton. Je suis gêné. C'est une erreur. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé. Voici le torchon. Je veux réparer. Nino essuie la table. Le torchon devient plus lourd. La flaque disparaît. La table redevient sèche. Merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer. Bravo, Nino. Plus tard, le salon est calme. Un puzzle attend sur le tapis. Une pièce bleue brille. Nino s'assoit près du puzzle. Son genou touche une pièce. La pièce tombe sur le tapis. Les joues de Nino chauffent encore. Je suis gêné. J'ai bougé la pièce. C'est une erreur. On peut la dire. Puis réparer. Je veux réparer. Nino pose la pièce à sa place. Le bleu retrouve le bleu. Tu as dit. Tu as réparé. Même leçon, autre pièce. On dit. On répare. Le puzzle redevient entier. La buée sèche un peu, là-bas.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1379,7 +1379,6 @@
 narrateur|La buée sèche un peu, là-bas.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1409,7 +1408,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Georges a les joues chaudes. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a les joues chaudes. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1564,7 +1563,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1589,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino était gêné. Il a dit l'erreur. Il a réparé. Papa et maman ont écouté. J'ai versé. Puis j'ai essuyé. Oui. Tu as nommé : gêné. Puis tu as réparé le puzzle. Bravo. C'est du bon travail. L'erreur n'est pas moi. C'est ça. L'erreur, on la dit. Le torchon est plié sur la table. La pièce bleue est à sa place. On dit. On répare. Deux fois. L'eau, puis la pièce. Même leçon, autre moment. La soupe sent encore, tout doux.</t>
+          <t>Nino était gêné. Il a dit l'erreur. Il a réparé. Papa et maman ont écouté. J'ai versé. Puis j'ai essuyé. Oui. Tu as nommé : gêné. Puis tu as réparé le puzzle. L'erreur n'est pas moi. C'est ça. L'erreur, on la dit. Le torchon est plié sur la table. La pièce bleue est à sa place. On dit. On répare. Deux fois. L'eau, puis la pièce. Même leçon, autre moment. La soupe sent encore, tout doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Georges était &lt;emphasis level="moderate"&gt;gêné&lt;/emphasis&gt;. Il a dit l'erreur. Il a réparé. Papa et maman ont écouté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino était gêné. Il a dit l'erreur. Il a réparé. Papa et maman ont écouté. J'ai versé. Puis j'ai essuyé. Oui. Tu as nommé : gêné. Puis tu as réparé le puzzle. L'erreur n'est pas moi. C'est ça. L'erreur, on la dit. Le torchon est plié sur la table. La pièce bleue est à sa place. On dit. On répare. Deux fois. L'eau, puis la pièce. Même leçon, autre moment. La soupe sent encore, tout doux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1740,7 +1738,6 @@
 enfant-m|J'ai versé. Puis j'ai essuyé.
 papa|Oui. Tu as nommé : gêné.
 maman|Puis tu as réparé le puzzle.
-papa|Bravo. C'est du bon travail.
 enfant-m|L'erreur n'est pas moi.
 maman|C'est ça. L'erreur, on la dit.
 narrateur|Le torchon est plié sur la table.
@@ -1751,7 +1748,6 @@
 narrateur|La soupe sent encore, tout doux.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1781,7 +1777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Georges plie le chiffon. Le puzzle est de nouveau entier.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino plie le torchon. Le puzzle est de nouveau entier. On pose le torchon près de l'évier ? Oui, papa. La table est sèche. Merci, Nino. J'ai réparé. Tu as dit, aussi. On goûte la soupe, tout à l'heure ? Oui. Elle sent bon. Nino touche la pièce bleue. Elle est un peu rugueuse. Elle est à sa place. Je suis moins gêné. On a réparé. C'est bien. La buée a presque disparu. Un rond clair est sur la vitre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1930,7 +1926,6 @@
 narrateur|Un rond clair est sur la vitre.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1955,12 +1950,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais gêné. J'ai dit. Tu as réparé. Bravo. L'eau, puis la pièce. Pareil. Le torchon reste plié. L'histoire est finie.</t>
+          <t>J'étais gêné. J'ai dit. Tu as réparé. Bravo. L'eau, puis la pièce. Pareil. Le torchon reste plié.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais gêné. J'ai dit. Tu as réparé. Bravo. L'eau, puis la pièce. Pareil. Le torchon reste plié.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2098,11 +2093,9 @@
           <t>enfant-m|J'étais gêné. J'ai dit.
 papa|Tu as réparé. Bravo.
 maman|L'eau, puis la pièce. Pareil.
-narrateur|Le torchon reste plié.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le torchon reste plié.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2121,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2166,6 +2159,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Georges, papa, maman</t>
+          <t>Nino, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.008-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.008-07.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nino verse de l'eau. Il dit qu'il est gêné. Il répare. Plus tard, une pièce de puzzle. Il dit encore. Il répare.</t>
+          <t>Nino veut verser l'eau pour la soupe. Le verre penche. Il dit qu'il est gêné, essuie. Au salon, une pièce tombe. Il la remet. La soupe fume. Le bleu retrouve le bleu.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la cuisine a de la buée. Un doigt y a dessiné une petite goutte. Ça sent la soupe, tout chaud. La bouilloire fait tic, tic, tic. Un torchon humide pend au dossier. La table a un tapis à carreaux. La soupe est presque prête, Nino. On met l'eau, tout doucement. La vitre est floue, papa. C'est la buée. C'est chaud. Tu portes le petit verre ? Oui. Il est froid. On reste près de la table. En ce moment, Nino verse l'eau. Le verre penche. L'eau glisse sur le tapis à carreaux. Une flaque ronde brille. Nino sent ses joues chaudes. Il baisse un peu le menton. Je suis gêné. C'est une erreur. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé. Voici le torchon. Je veux réparer. Nino essuie la table. Le torchon devient plus lourd. La flaque disparaît. La table redevient sèche. Merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer. Bravo, Nino. Plus tard, le salon est calme. Un puzzle attend sur le tapis. Une pièce bleue brille. Nino s'assoit près du puzzle. Son genou touche une pièce. La pièce tombe sur le tapis. Les joues de Nino chauffent encore. Je suis gêné. J'ai bougé la pièce. C'est une erreur. On peut la dire. Puis réparer. Je veux réparer. Nino pose la pièce à sa place. Le bleu retrouve le bleu. Tu as dit. Tu as réparé. Même leçon, autre pièce. On dit. On répare. Le puzzle redevient entier. La buée sèche un peu, là-bas.</t>
+          <t>La vitre de la cuisine a de la buée. Un doigt y a dessiné une petite goutte. Ça sent la soupe, tout chaud. La bouilloire fait tic, tic, tic. Un torchon humide pend au dossier. La table a un tapis à carreaux. La soupe est presque prête, Nino. On met l'eau, tout doucement. La vitre est floue, papa. C'est la buée. Tu portes le petit verre ? Oui. Il est froid. On reste près de la table ? Oui. Je veux verser. En ce moment, Nino verse l'eau. Le verre penche. L'eau glisse sur le tapis à carreaux. Une flaque ronde brille. Nino sent ses joues chaudes. Il baisse un peu le menton. Je suis gêné. J'ai versé. Ce n'est pas grave. Le torchon est là, Nino. Je veux essuyer. Nino essuie la table. Le torchon devient plus lourd. La flaque disparaît. La table redevient sèche. Merci d'avoir dit, Nino. J'ai essuyé. Oui. Plus tard, le salon est calme. Un puzzle attend sur le tapis. Une pièce bleue brille. Je veux le ciel, là. Elle est un peu rugueuse. Nino s'assoit près du puzzle. Son genou touche une pièce. La pièce tombe sur le tapis. Les joues de Nino chauffent encore. La pièce est tombée. On la voit, près de toi. Je la remets. Nino pose la pièce à sa place. Le bleu retrouve le bleu. Elle tient, maintenant. Oui. La soupe sent encore, tu trouves ? Oui. Tout chaud. Le torchon reste un peu lourd. La buée sèche un peu, là-bas.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La vitre de la cuisine a de la buée. Un doigt y a dessiné une petite goutte. Ça sent la soupe, tout chaud. La bouilloire fait tic, tic, tic. Un torchon humide pend au dossier. La table a un tapis à carreaux. La soupe est presque prête, Nino. On met l'eau, tout doucement. La vitre est floue, papa. C'est la buée. C'est chaud. Tu portes le petit verre ? Oui. Il est froid. On reste près de la table. En ce moment, Nino verse l'eau. Le verre penche. L'eau glisse sur le tapis à carreaux. Une flaque ronde brille. Nino sent ses joues chaudes. Il baisse un peu le menton. Je suis gêné. C'est une erreur. Une erreur, ce n'est pas toi. L'erreur, on peut la dire. J'ai versé. Voici le torchon. Je veux réparer. Nino essuie la table. Le torchon devient plus lourd. La flaque disparaît. La table redevient sèche. Merci d'avoir dit. Être gêné, on le dit. Puis on peut réparer. Bravo, Nino. Plus tard, le salon est calme. Un puzzle attend sur le tapis. Une pièce bleue brille. Nino s'assoit près du puzzle. Son genou touche une pièce. La pièce tombe sur le tapis. Les joues de Nino chauffent encore. Je suis gêné. J'ai bougé la pièce. C'est une erreur. On peut la dire. Puis réparer. Je veux réparer. Nino pose la pièce à sa place. Le bleu retrouve le bleu. Tu as dit. Tu as réparé. Même leçon, autre pièce. On dit. On répare. Le puzzle redevient entier. La buée sèche un peu, là-bas.</t>
+          <t>La vitre de la cuisine a de la buée. Un doigt y a dessiné une petite goutte. Ça sent la soupe, tout chaud. La bouilloire fait tic, tic, tic. Un torchon humide pend au dossier. La table a un tapis à carreaux. La soupe est presque prête, Nino. On met l'eau, tout doucement. La vitre est floue, papa. C'est la buée. Tu portes le petit verre ? Oui. Il est froid. On reste près de la table ? Oui. Je veux verser. En ce moment, Nino verse l'eau. Le verre penche. L'eau glisse sur le tapis à carreaux. Une flaque ronde brille. Nino sent ses joues chaudes. Il baisse un peu le menton. Je suis gêné. J'ai versé. Ce n'est pas grave. Le torchon est là, Nino. Je veux essuyer. Nino essuie la table. Le torchon devient plus lourd. La flaque disparaît. La table redevient sèche. Merci d'avoir dit, Nino. J'ai essuyé. Oui. Plus tard, le salon est calme. Un puzzle attend sur le tapis. Une pièce bleue brille. Je veux le ciel, là. Elle est un peu rugueuse. Nino s'assoit près du puzzle. Son genou touche une pièce. La pièce tombe sur le tapis. Les joues de Nino chauffent encore. La pièce est tombée. On la voit, près de toi. Je la remets. Nino pose la pièce à sa place. Le bleu retrouve le bleu. Elle tient, maintenant. Oui. La soupe sent encore, tu trouves ? Oui. Tout chaud. Le torchon reste un peu lourd. La buée sèche un peu, là-bas.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1245,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1333,10 +1333,13 @@
 maman|La soupe est presque prête, Nino.
 papa|On met l'eau, tout doucement.
 enfant-m|La vitre est floue, papa.
-papa|C'est la buée. C'est chaud.
+papa|C'est la buée.
 maman|Tu portes le petit verre ?
-enfant-m|Oui. Il est froid.
-papa|On reste près de la table.
+enfant-m|Oui.
+enfant-m|Il est froid.
+papa|On reste près de la table ?
+enfant-m|Oui.
+enfant-m|Je veux verser.
 narrateur|En ce moment, Nino verse l'eau.
 narrateur|Le verre penche.
 narrateur|L'eau glisse sur le tapis à carreaux.
@@ -1344,38 +1347,37 @@
 narrateur|Nino sent ses joues chaudes.
 narrateur|Il baisse un peu le menton.
 enfant-m|Je suis gêné.
-papa|C'est une erreur.
-papa|Une erreur, ce n'est pas toi.
-maman|L'erreur, on peut la dire.
 enfant-m|J'ai versé.
-papa|Voici le torchon.
-enfant-m|Je veux réparer.
+papa|Ce n'est pas grave.
+maman|Le torchon est là, Nino.
+enfant-m|Je veux essuyer.
 narrateur|Nino essuie la table.
 narrateur|Le torchon devient plus lourd.
 narrateur|La flaque disparaît.
 maman|La table redevient sèche.
-papa|Merci d'avoir dit.
-papa|Être gêné, on le dit.
-maman|Puis on peut réparer.
-papa|Bravo, Nino.
+papa|Merci d'avoir dit, Nino.
+enfant-m|J'ai essuyé.
+papa|Oui.
 narrateur|Plus tard, le salon est calme.
 narrateur|Un puzzle attend sur le tapis.
 narrateur|Une pièce bleue brille.
+enfant-m|Je veux le ciel, là.
+maman|Elle est un peu rugueuse.
 narrateur|Nino s'assoit près du puzzle.
 narrateur|Son genou touche une pièce.
 narrateur|La pièce tombe sur le tapis.
 narrateur|Les joues de Nino chauffent encore.
-enfant-m|Je suis gêné.
-enfant-m|J'ai bougé la pièce.
-maman|C'est une erreur.
-papa|On peut la dire. Puis réparer.
-enfant-m|Je veux réparer.
+enfant-m|La pièce est tombée.
+papa|On la voit, près de toi.
+enfant-m|Je la remets.
 narrateur|Nino pose la pièce à sa place.
 narrateur|Le bleu retrouve le bleu.
-maman|Tu as dit. Tu as réparé.
-papa|Même leçon, autre pièce.
-enfant-m|On dit. On répare.
-narrateur|Le puzzle redevient entier.
+maman|Elle tient, maintenant.
+enfant-m|Oui.
+papa|La soupe sent encore, tu trouves ?
+enfant-m|Oui.
+enfant-m|Tout chaud.
+narrateur|Le torchon reste un peu lourd.
 narrateur|La buée sèche un peu, là-bas.</t>
         </is>
       </c>
@@ -1423,7 +1425,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>gêné | je suis gêné | réparer | il répare | une erreur</t>
+          <t>gêné | je suis gêné | réparer | il répare | une erreur | essuyer</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1438,7 +1440,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il dit qu'il est gêné. Puis il répare. Que fait Georges ?</t>
+          <t>Nino a versé. Que dit-il, puis que fait-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1487,7 +1489,7 @@
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1587,12 +1589,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino était gêné. Il a dit l'erreur. Il a réparé. Papa et maman ont écouté. J'ai versé. Puis j'ai essuyé. Oui. Tu as nommé : gêné. Puis tu as réparé le puzzle. L'erreur n'est pas moi. C'est ça. L'erreur, on la dit. Le torchon est plié sur la table. La pièce bleue est à sa place. On dit. On répare. Deux fois. L'eau, puis la pièce. Même leçon, autre moment. La soupe sent encore, tout doux.</t>
+          <t>Nino plie le torchon. Le puzzle est de nouveau entier. On pose le torchon près de l'évier ? Oui, papa. La table est sèche. Bravo, Nino. J'ai essuyé. La pièce bleue aussi est rentrée. Le torchon est plié sur la table. La soupe sent encore, tout doux.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nino était gêné. Il a dit l'erreur. Il a réparé. Papa et maman ont écouté. J'ai versé. Puis j'ai essuyé. Oui. Tu as nommé : gêné. Puis tu as réparé le puzzle. L'erreur n'est pas moi. C'est ça. L'erreur, on la dit. Le torchon est plié sur la table. La pièce bleue est à sa place. On dit. On répare. Deux fois. L'eau, puis la pièce. Même leçon, autre moment. La soupe sent encore, tout doux.</t>
+          <t>Nino plie le torchon. Le puzzle est de nouveau entier. On pose le torchon près de l'évier ? Oui, papa. La table est sèche. Bravo, Nino. J'ai essuyé. La pièce bleue aussi est rentrée. Le torchon est plié sur la table. La soupe sent encore, tout doux.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1648,14 +1650,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1731,20 +1733,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nino était gêné.
-narrateur|Il a dit l'erreur.
-narrateur|Il a réparé.
-narrateur|Papa et maman ont écouté.
-enfant-m|J'ai versé. Puis j'ai essuyé.
-papa|Oui. Tu as nommé : gêné.
-maman|Puis tu as réparé le puzzle.
-enfant-m|L'erreur n'est pas moi.
-maman|C'est ça. L'erreur, on la dit.
+          <t>narrateur|Nino plie le torchon.
+narrateur|Le puzzle est de nouveau entier.
+papa|On pose le torchon près de l'évier ?
+enfant-m|Oui, papa.
+maman|La table est sèche.
+maman|Bravo, Nino.
+enfant-m|J'ai essuyé.
+papa|La pièce bleue aussi est rentrée.
 narrateur|Le torchon est plié sur la table.
-narrateur|La pièce bleue est à sa place.
-papa|On dit. On répare.
-enfant-m|Deux fois. L'eau, puis la pièce.
-maman|Même leçon, autre moment.
 narrateur|La soupe sent encore, tout doux.</t>
         </is>
       </c>
@@ -1772,12 +1769,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nino plie le torchon. Le puzzle est de nouveau entier. On pose le torchon près de l'évier ? Oui, papa. La table est sèche. Merci, Nino. J'ai réparé. Tu as dit, aussi. On goûte la soupe, tout à l'heure ? Oui. Elle sent bon. Nino touche la pièce bleue. Elle est un peu rugueuse. Elle est à sa place. Je suis moins gêné. On a réparé. C'est bien. La buée a presque disparu. Un rond clair est sur la vitre.</t>
+          <t>Nino touche la pièce bleue. Elle est un peu rugueuse. On goûte la soupe, tout à l'heure ? Oui. Elle sent bon. Le verre est vide, maintenant. Je suis moins chaud. La table est sèche. La buée a presque disparu. Un rond clair est sur la vitre.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Nino plie le torchon. Le puzzle est de nouveau entier. On pose le torchon près de l'évier ? Oui, papa. La table est sèche. Merci, Nino. J'ai réparé. Tu as dit, aussi. On goûte la soupe, tout à l'heure ? Oui. Elle sent bon. Nino touche la pièce bleue. Elle est un peu rugueuse. Elle est à sa place. Je suis moins gêné. On a réparé. C'est bien. La buée a presque disparu. Un rond clair est sur la vitre.</t>
+          <t>Nino touche la pièce bleue. Elle est un peu rugueuse. On goûte la soupe, tout à l'heure ? Oui. Elle sent bon. Le verre est vide, maintenant. Je suis moins chaud. La table est sèche. La buée a presque disparu. Un rond clair est sur la vitre.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1833,14 +1830,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1908,20 +1905,14 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nino plie le torchon.
-narrateur|Le puzzle est de nouveau entier.
-papa|On pose le torchon près de l'évier ?
-enfant-m|Oui, papa.
-maman|La table est sèche. Merci, Nino.
-enfant-m|J'ai réparé.
-papa|Tu as dit, aussi.
+          <t>narrateur|Nino touche la pièce bleue.
+narrateur|Elle est un peu rugueuse.
 maman|On goûte la soupe, tout à l'heure ?
-enfant-m|Oui. Elle sent bon.
-narrateur|Nino touche la pièce bleue.
-narrateur|Elle est un peu rugueuse.
-papa|Elle est à sa place.
-enfant-m|Je suis moins gêné.
-maman|On a réparé. C'est bien.
+enfant-m|Oui.
+enfant-m|Elle sent bon.
+papa|Le verre est vide, maintenant.
+enfant-m|Je suis moins chaud.
+maman|La table est sèche.
 narrateur|La buée a presque disparu.
 narrateur|Un rond clair est sur la vitre.</t>
         </is>
@@ -1950,12 +1941,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais gêné. J'ai dit. Tu as réparé. Bravo. L'eau, puis la pièce. Pareil. Le torchon reste plié.</t>
+          <t>La table est sèche. Merci, Nino. La pièce bleue reste à sa place. La soupe fume encore, tout doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'étais gêné. J'ai dit. Tu as réparé. Bravo. L'eau, puis la pièce. Pareil. Le torchon reste plié.</t>
+          <t>La table est sèche. Merci, Nino. La pièce bleue reste à sa place. La soupe fume encore, tout doux.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2011,14 +2002,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2090,10 +2081,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'étais gêné. J'ai dit.
-papa|Tu as réparé. Bravo.
-maman|L'eau, puis la pièce. Pareil.
-narrateur|Le torchon reste plié.</t>
+          <t>enfant-m|La table est sèche.
+papa|Merci, Nino.
+narrateur|La pièce bleue reste à sa place.
+narrateur|La soupe fume encore, tout doux.</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2164,6 +2155,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
